--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -15359,7 +15359,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de matrícula población de 0 a 24 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -2104,7 +2104,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:35</t>
+    <t xml:space="preserve">2026-09-07 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -2104,7 +2104,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:48</t>
+    <t xml:space="preserve">2026-09-08 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
